--- a/artfynd/A 4005-2025 artfynd.xlsx
+++ b/artfynd/A 4005-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122847371</v>
+        <v>122846952</v>
       </c>
       <c r="B2" t="n">
-        <v>90958</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582809</v>
+        <v>582892</v>
       </c>
       <c r="R2" t="n">
-        <v>7041285</v>
+        <v>7041245</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122847763</v>
+        <v>122847974</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +813,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582749</v>
+        <v>582679</v>
       </c>
       <c r="R3" t="n">
-        <v>7041278</v>
+        <v>7041287</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122846952</v>
+        <v>122846482</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -940,7 +945,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -949,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582892</v>
+        <v>582919</v>
       </c>
       <c r="R4" t="n">
-        <v>7041245</v>
+        <v>7041138</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1014,22 +1019,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122846792</v>
+        <v>122847452</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,39 +1047,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582913</v>
+        <v>582796</v>
       </c>
       <c r="R5" t="n">
-        <v>7041182</v>
+        <v>7041306</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,12 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122847452</v>
+        <v>122847371</v>
       </c>
       <c r="B6" t="n">
-        <v>82549</v>
+        <v>90962</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,21 +1159,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1188,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582796</v>
+        <v>582809</v>
       </c>
       <c r="R6" t="n">
-        <v>7041306</v>
+        <v>7041285</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122846313</v>
+        <v>122847763</v>
       </c>
       <c r="B7" t="n">
-        <v>78762</v>
+        <v>57494</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,34 +1271,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582953</v>
+        <v>582749</v>
       </c>
       <c r="R7" t="n">
-        <v>7041141</v>
+        <v>7041278</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122847974</v>
+        <v>122846792</v>
       </c>
       <c r="B8" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,34 +1388,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582679</v>
+        <v>582913</v>
       </c>
       <c r="R8" t="n">
-        <v>7041287</v>
+        <v>7041182</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1462,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1601,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122846482</v>
+        <v>122846313</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,39 +1627,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582919</v>
+        <v>582953</v>
       </c>
       <c r="R10" t="n">
-        <v>7041138</v>
+        <v>7041141</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,12 +1696,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 4005-2025 artfynd.xlsx
+++ b/artfynd/A 4005-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122846952</v>
+        <v>122846482</v>
       </c>
       <c r="B2" t="n">
         <v>57478</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582892</v>
+        <v>582919</v>
       </c>
       <c r="R2" t="n">
-        <v>7041245</v>
+        <v>7041138</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -785,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122847974</v>
+        <v>122847371</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,21 +813,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582679</v>
+        <v>582809</v>
       </c>
       <c r="R3" t="n">
-        <v>7041287</v>
+        <v>7041285</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122846482</v>
+        <v>122846313</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,39 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582919</v>
+        <v>582953</v>
       </c>
       <c r="R4" t="n">
-        <v>7041138</v>
+        <v>7041141</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122847452</v>
+        <v>122847763</v>
       </c>
       <c r="B5" t="n">
-        <v>82553</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,34 +1037,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582796</v>
+        <v>582749</v>
       </c>
       <c r="R5" t="n">
-        <v>7041306</v>
+        <v>7041278</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122847371</v>
+        <v>122847452</v>
       </c>
       <c r="B6" t="n">
-        <v>90962</v>
+        <v>82553</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,21 +1154,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582809</v>
+        <v>582796</v>
       </c>
       <c r="R6" t="n">
-        <v>7041285</v>
+        <v>7041306</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122847763</v>
+        <v>122847974</v>
       </c>
       <c r="B7" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,39 +1266,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582749</v>
+        <v>582679</v>
       </c>
       <c r="R7" t="n">
-        <v>7041278</v>
+        <v>7041287</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1494,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122846587</v>
+        <v>122846952</v>
       </c>
       <c r="B9" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,16 +1500,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1539,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582893</v>
+        <v>582892</v>
       </c>
       <c r="R9" t="n">
-        <v>7041163</v>
+        <v>7041245</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1574,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1574,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,10 +1606,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122846313</v>
+        <v>122846587</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,34 +1622,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582953</v>
+        <v>582893</v>
       </c>
       <c r="R10" t="n">
-        <v>7041141</v>
+        <v>7041163</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,12 +1711,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 4005-2025 artfynd.xlsx
+++ b/artfynd/A 4005-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122846482</v>
+        <v>122847371</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582919</v>
+        <v>582809</v>
       </c>
       <c r="R2" t="n">
-        <v>7041138</v>
+        <v>7041285</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122847371</v>
+        <v>122846952</v>
       </c>
       <c r="B3" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582809</v>
+        <v>582892</v>
       </c>
       <c r="R3" t="n">
-        <v>7041285</v>
+        <v>7041245</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122846313</v>
+        <v>122846587</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,34 +925,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582953</v>
+        <v>582893</v>
       </c>
       <c r="R4" t="n">
-        <v>7041141</v>
+        <v>7041163</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +1014,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122847763</v>
+        <v>122847452</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>82553</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,39 +1042,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582749</v>
+        <v>582796</v>
       </c>
       <c r="R5" t="n">
-        <v>7041278</v>
+        <v>7041306</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122847452</v>
+        <v>122847763</v>
       </c>
       <c r="B6" t="n">
-        <v>82553</v>
+        <v>57494</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,34 +1154,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582796</v>
+        <v>582749</v>
       </c>
       <c r="R6" t="n">
-        <v>7041306</v>
+        <v>7041278</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1484,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122846952</v>
+        <v>122846313</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,39 +1505,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582892</v>
+        <v>582953</v>
       </c>
       <c r="R9" t="n">
-        <v>7041245</v>
+        <v>7041141</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,12 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:51</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,22 +1589,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122846587</v>
+        <v>122846482</v>
       </c>
       <c r="B10" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,16 +1617,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1642,7 +1637,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1651,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582893</v>
+        <v>582919</v>
       </c>
       <c r="R10" t="n">
-        <v>7041163</v>
+        <v>7041138</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1699,6 +1694,11 @@
           <t>15:38</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1711,12 +1711,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 4005-2025 artfynd.xlsx
+++ b/artfynd/A 4005-2025 artfynd.xlsx
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122847974</v>
+        <v>122846792</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,34 +1271,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582679</v>
+        <v>582913</v>
       </c>
       <c r="R7" t="n">
-        <v>7041287</v>
+        <v>7041182</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1345,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122846792</v>
+        <v>122847974</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,39 +1393,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582913</v>
+        <v>582679</v>
       </c>
       <c r="R8" t="n">
-        <v>7041182</v>
+        <v>7041287</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,12 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 4005-2025 artfynd.xlsx
+++ b/artfynd/A 4005-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122847371</v>
+        <v>122846587</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582809</v>
+        <v>582893</v>
       </c>
       <c r="R2" t="n">
-        <v>7041285</v>
+        <v>7041163</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122846952</v>
+        <v>122847974</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582892</v>
+        <v>582679</v>
       </c>
       <c r="R3" t="n">
-        <v>7041245</v>
+        <v>7041287</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:51</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +892,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122846587</v>
+        <v>122847452</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>82553</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582893</v>
+        <v>582796</v>
       </c>
       <c r="R4" t="n">
-        <v>7041163</v>
+        <v>7041306</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,22 +1004,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122847452</v>
+        <v>122847763</v>
       </c>
       <c r="B5" t="n">
-        <v>82553</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,34 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582796</v>
+        <v>582749</v>
       </c>
       <c r="R5" t="n">
-        <v>7041306</v>
+        <v>7041278</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122847763</v>
+        <v>122846792</v>
       </c>
       <c r="B6" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,16 +1149,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1174,7 +1169,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1183,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582749</v>
+        <v>582913</v>
       </c>
       <c r="R6" t="n">
-        <v>7041278</v>
+        <v>7041182</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1223,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122846792</v>
+        <v>122847371</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,39 +1271,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582913</v>
+        <v>582809</v>
       </c>
       <c r="R7" t="n">
-        <v>7041182</v>
+        <v>7041285</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,12 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,7 +1367,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122847974</v>
+        <v>122846313</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1417,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582679</v>
+        <v>582953</v>
       </c>
       <c r="R8" t="n">
-        <v>7041287</v>
+        <v>7041141</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122846313</v>
+        <v>122846952</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,34 +1495,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582953</v>
+        <v>582892</v>
       </c>
       <c r="R9" t="n">
-        <v>7041141</v>
+        <v>7041245</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1569,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,12 +1589,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 4005-2025 artfynd.xlsx
+++ b/artfynd/A 4005-2025 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122847763</v>
+        <v>122846792</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,16 +1032,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1052,7 +1052,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582749</v>
+        <v>582913</v>
       </c>
       <c r="R5" t="n">
-        <v>7041278</v>
+        <v>7041182</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122846792</v>
+        <v>122847763</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,16 +1154,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1169,7 +1174,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1178,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582913</v>
+        <v>582749</v>
       </c>
       <c r="R6" t="n">
-        <v>7041182</v>
+        <v>7041278</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,12 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 4005-2025 artfynd.xlsx
+++ b/artfynd/A 4005-2025 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122846792</v>
+        <v>122847763</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,16 +1032,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1052,7 +1052,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582913</v>
+        <v>582749</v>
       </c>
       <c r="R5" t="n">
-        <v>7041182</v>
+        <v>7041278</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122847763</v>
+        <v>122846792</v>
       </c>
       <c r="B6" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,16 +1149,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1174,7 +1169,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1183,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582749</v>
+        <v>582913</v>
       </c>
       <c r="R6" t="n">
-        <v>7041278</v>
+        <v>7041182</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1223,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 4005-2025 artfynd.xlsx
+++ b/artfynd/A 4005-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122846587</v>
+        <v>122846482</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582893</v>
+        <v>582919</v>
       </c>
       <c r="R2" t="n">
-        <v>7041163</v>
+        <v>7041138</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,6 +768,11 @@
           <t>15:38</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -780,12 +785,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122847452</v>
+        <v>122846587</v>
       </c>
       <c r="B4" t="n">
-        <v>82553</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +925,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582796</v>
+        <v>582893</v>
       </c>
       <c r="R4" t="n">
-        <v>7041306</v>
+        <v>7041163</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,22 +1014,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122847763</v>
+        <v>122846313</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,39 +1042,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582749</v>
+        <v>582953</v>
       </c>
       <c r="R5" t="n">
-        <v>7041278</v>
+        <v>7041141</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122846792</v>
+        <v>122847371</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,39 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582913</v>
+        <v>582809</v>
       </c>
       <c r="R6" t="n">
-        <v>7041182</v>
+        <v>7041285</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,12 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122847371</v>
+        <v>122847452</v>
       </c>
       <c r="B7" t="n">
-        <v>90962</v>
+        <v>82553</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582809</v>
+        <v>582796</v>
       </c>
       <c r="R7" t="n">
-        <v>7041285</v>
+        <v>7041306</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122846313</v>
+        <v>122847763</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,34 +1378,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582953</v>
+        <v>582749</v>
       </c>
       <c r="R8" t="n">
-        <v>7041141</v>
+        <v>7041278</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122846952</v>
+        <v>122846792</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1515,7 +1515,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582892</v>
+        <v>582913</v>
       </c>
       <c r="R9" t="n">
-        <v>7041245</v>
+        <v>7041182</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1589,19 +1589,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122846482</v>
+        <v>122846952</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1637,7 +1637,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582919</v>
+        <v>582892</v>
       </c>
       <c r="R10" t="n">
-        <v>7041138</v>
+        <v>7041245</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1711,12 +1711,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 4005-2025 artfynd.xlsx
+++ b/artfynd/A 4005-2025 artfynd.xlsx
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122847452</v>
+        <v>122847763</v>
       </c>
       <c r="B7" t="n">
-        <v>82553</v>
+        <v>57494</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,34 +1266,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582796</v>
+        <v>582749</v>
       </c>
       <c r="R7" t="n">
-        <v>7041306</v>
+        <v>7041278</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122847763</v>
+        <v>122847452</v>
       </c>
       <c r="B8" t="n">
-        <v>57494</v>
+        <v>82553</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,39 +1383,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582749</v>
+        <v>582796</v>
       </c>
       <c r="R8" t="n">
-        <v>7041278</v>
+        <v>7041306</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 4005-2025 artfynd.xlsx
+++ b/artfynd/A 4005-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122846482</v>
+        <v>122847763</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582919</v>
+        <v>582749</v>
       </c>
       <c r="R2" t="n">
-        <v>7041138</v>
+        <v>7041278</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -909,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122846587</v>
+        <v>122847452</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>82553</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582893</v>
+        <v>582796</v>
       </c>
       <c r="R4" t="n">
-        <v>7041163</v>
+        <v>7041306</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,22 +1004,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122846313</v>
+        <v>122846587</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,34 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582953</v>
+        <v>582893</v>
       </c>
       <c r="R5" t="n">
-        <v>7041141</v>
+        <v>7041163</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,22 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122847371</v>
+        <v>122846313</v>
       </c>
       <c r="B6" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582809</v>
+        <v>582953</v>
       </c>
       <c r="R6" t="n">
-        <v>7041285</v>
+        <v>7041141</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122847763</v>
+        <v>122847371</v>
       </c>
       <c r="B7" t="n">
-        <v>57494</v>
+        <v>90970</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,39 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582749</v>
+        <v>582809</v>
       </c>
       <c r="R7" t="n">
-        <v>7041278</v>
+        <v>7041285</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122847452</v>
+        <v>122846482</v>
       </c>
       <c r="B8" t="n">
-        <v>82553</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,34 +1373,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582796</v>
+        <v>582919</v>
       </c>
       <c r="R8" t="n">
-        <v>7041306</v>
+        <v>7041138</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1447,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122846792</v>
+        <v>122846952</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1515,7 +1515,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582913</v>
+        <v>582892</v>
       </c>
       <c r="R9" t="n">
-        <v>7041182</v>
+        <v>7041245</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1589,19 +1589,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122846952</v>
+        <v>122846792</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1637,7 +1637,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582892</v>
+        <v>582913</v>
       </c>
       <c r="R10" t="n">
-        <v>7041245</v>
+        <v>7041182</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1711,12 +1711,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 4005-2025 artfynd.xlsx
+++ b/artfynd/A 4005-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1721,6 +1721,118 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123271869</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>582830</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7041034</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4005-2025 artfynd.xlsx
+++ b/artfynd/A 4005-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122847763</v>
+        <v>122847974</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582749</v>
+        <v>582679</v>
       </c>
       <c r="R2" t="n">
-        <v>7041278</v>
+        <v>7041287</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122847974</v>
+        <v>122847371</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582679</v>
+        <v>582809</v>
       </c>
       <c r="R3" t="n">
-        <v>7041287</v>
+        <v>7041285</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1016,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122846587</v>
+        <v>122847763</v>
       </c>
       <c r="B5" t="n">
         <v>57494</v>
@@ -1061,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582893</v>
+        <v>582749</v>
       </c>
       <c r="R5" t="n">
-        <v>7041163</v>
+        <v>7041278</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,22 +1116,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122846313</v>
+        <v>122846587</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,34 +1144,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582953</v>
+        <v>582893</v>
       </c>
       <c r="R6" t="n">
-        <v>7041141</v>
+        <v>7041163</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,22 +1233,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122847371</v>
+        <v>122846792</v>
       </c>
       <c r="B7" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,34 +1261,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582809</v>
+        <v>582913</v>
       </c>
       <c r="R7" t="n">
-        <v>7041285</v>
+        <v>7041182</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1335,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,7 +1367,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122846482</v>
+        <v>122846952</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1393,7 +1403,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1402,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582919</v>
+        <v>582892</v>
       </c>
       <c r="R8" t="n">
-        <v>7041138</v>
+        <v>7041245</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1467,22 +1477,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122846952</v>
+        <v>122846313</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,39 +1505,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582892</v>
+        <v>582953</v>
       </c>
       <c r="R9" t="n">
-        <v>7041245</v>
+        <v>7041141</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,12 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:51</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,19 +1589,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122846792</v>
+        <v>122846482</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582913</v>
+        <v>582919</v>
       </c>
       <c r="R10" t="n">
-        <v>7041182</v>
+        <v>7041138</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">

--- a/artfynd/A 4005-2025 artfynd.xlsx
+++ b/artfynd/A 4005-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122847974</v>
+        <v>122846952</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582679</v>
+        <v>582892</v>
       </c>
       <c r="R2" t="n">
-        <v>7041287</v>
+        <v>7041245</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122847371</v>
+        <v>122847974</v>
       </c>
       <c r="B3" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +813,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582809</v>
+        <v>582679</v>
       </c>
       <c r="R3" t="n">
-        <v>7041285</v>
+        <v>7041287</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122847452</v>
+        <v>122846587</v>
       </c>
       <c r="B4" t="n">
-        <v>82553</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +925,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582796</v>
+        <v>582893</v>
       </c>
       <c r="R4" t="n">
-        <v>7041306</v>
+        <v>7041163</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +1014,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122847763</v>
+        <v>122847452</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>82553</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,39 +1042,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582749</v>
+        <v>582796</v>
       </c>
       <c r="R5" t="n">
-        <v>7041278</v>
+        <v>7041306</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122846587</v>
+        <v>122846313</v>
       </c>
       <c r="B6" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,39 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582893</v>
+        <v>582953</v>
       </c>
       <c r="R6" t="n">
-        <v>7041163</v>
+        <v>7041141</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,19 +1238,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122846792</v>
+        <v>122846482</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1290,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582913</v>
+        <v>582919</v>
       </c>
       <c r="R7" t="n">
-        <v>7041182</v>
+        <v>7041138</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1367,7 +1372,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122846952</v>
+        <v>122846792</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1403,7 +1408,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1412,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582892</v>
+        <v>582913</v>
       </c>
       <c r="R8" t="n">
-        <v>7041245</v>
+        <v>7041182</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1477,22 +1482,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122846313</v>
+        <v>122847763</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,34 +1510,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582953</v>
+        <v>582749</v>
       </c>
       <c r="R9" t="n">
-        <v>7041141</v>
+        <v>7041278</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1584,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122846482</v>
+        <v>122847371</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,39 +1627,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582919</v>
+        <v>582809</v>
       </c>
       <c r="R10" t="n">
-        <v>7041138</v>
+        <v>7041285</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,12 +1696,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 4005-2025 artfynd.xlsx
+++ b/artfynd/A 4005-2025 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122847452</v>
+        <v>122846313</v>
       </c>
       <c r="B5" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582796</v>
+        <v>582953</v>
       </c>
       <c r="R5" t="n">
-        <v>7041306</v>
+        <v>7041141</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122846313</v>
+        <v>122846482</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,34 +1154,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582953</v>
+        <v>582919</v>
       </c>
       <c r="R6" t="n">
-        <v>7041141</v>
+        <v>7041138</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1228,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,7 +1260,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122846482</v>
+        <v>122846792</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1295,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582919</v>
+        <v>582913</v>
       </c>
       <c r="R7" t="n">
-        <v>7041138</v>
+        <v>7041182</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1372,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122846792</v>
+        <v>122847452</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,39 +1398,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582913</v>
+        <v>582796</v>
       </c>
       <c r="R8" t="n">
-        <v>7041182</v>
+        <v>7041306</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,12 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 4005-2025 artfynd.xlsx
+++ b/artfynd/A 4005-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122846952</v>
+        <v>122847452</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>82556</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582892</v>
+        <v>582796</v>
       </c>
       <c r="R2" t="n">
-        <v>7041245</v>
+        <v>7041306</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:51</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,12 +775,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -800,7 +790,7 @@
         <v>122847974</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -909,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122846587</v>
+        <v>122847371</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>90973</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582893</v>
+        <v>582809</v>
       </c>
       <c r="R4" t="n">
-        <v>7041163</v>
+        <v>7041285</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122846313</v>
+        <v>122846482</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,34 +1027,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582953</v>
+        <v>582919</v>
       </c>
       <c r="R5" t="n">
-        <v>7041141</v>
+        <v>7041138</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1101,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122846482</v>
+        <v>122847763</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>57497</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,16 +1149,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1174,7 +1169,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1183,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582919</v>
+        <v>582749</v>
       </c>
       <c r="R6" t="n">
-        <v>7041138</v>
+        <v>7041278</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,12 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,7 +1253,7 @@
         <v>122846792</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1382,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122847452</v>
+        <v>122846313</v>
       </c>
       <c r="B8" t="n">
-        <v>82553</v>
+        <v>78769</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,21 +1388,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1422,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582796</v>
+        <v>582953</v>
       </c>
       <c r="R8" t="n">
-        <v>7041306</v>
+        <v>7041141</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122847763</v>
+        <v>122846587</v>
       </c>
       <c r="B9" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1539,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582749</v>
+        <v>582893</v>
       </c>
       <c r="R9" t="n">
-        <v>7041278</v>
+        <v>7041163</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1574,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,22 +1589,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122847371</v>
+        <v>122846952</v>
       </c>
       <c r="B10" t="n">
-        <v>90970</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,34 +1617,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582809</v>
+        <v>582892</v>
       </c>
       <c r="R10" t="n">
-        <v>7041285</v>
+        <v>7041245</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,7 +1691,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,12 +1711,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1726,7 +1726,7 @@
         <v>123271869</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 4005-2025 artfynd.xlsx
+++ b/artfynd/A 4005-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122847452</v>
+        <v>122846313</v>
       </c>
       <c r="B2" t="n">
-        <v>82556</v>
+        <v>78771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582796</v>
+        <v>582953</v>
       </c>
       <c r="R2" t="n">
-        <v>7041306</v>
+        <v>7041141</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122847974</v>
+        <v>122846482</v>
       </c>
       <c r="B3" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582679</v>
+        <v>582919</v>
       </c>
       <c r="R3" t="n">
-        <v>7041287</v>
+        <v>7041138</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122847371</v>
+        <v>122847974</v>
       </c>
       <c r="B4" t="n">
-        <v>90973</v>
+        <v>78771</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582809</v>
+        <v>582679</v>
       </c>
       <c r="R4" t="n">
-        <v>7041285</v>
+        <v>7041287</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122846482</v>
+        <v>122846587</v>
       </c>
       <c r="B5" t="n">
-        <v>57481</v>
+        <v>57497</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,16 +1037,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1047,7 +1057,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1056,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582919</v>
+        <v>582893</v>
       </c>
       <c r="R5" t="n">
-        <v>7041138</v>
+        <v>7041163</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,11 +1114,6 @@
           <t>15:38</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1121,22 +1126,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122847763</v>
+        <v>122846952</v>
       </c>
       <c r="B6" t="n">
-        <v>57497</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,16 +1154,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1178,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582749</v>
+        <v>582892</v>
       </c>
       <c r="R6" t="n">
-        <v>7041278</v>
+        <v>7041245</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1228,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,12 +1248,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1372,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122846313</v>
+        <v>122847763</v>
       </c>
       <c r="B8" t="n">
-        <v>78769</v>
+        <v>57497</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,34 +1398,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582953</v>
+        <v>582749</v>
       </c>
       <c r="R8" t="n">
-        <v>7041141</v>
+        <v>7041278</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1462,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1472,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,10 +1499,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122846587</v>
+        <v>122847452</v>
       </c>
       <c r="B9" t="n">
-        <v>57497</v>
+        <v>82558</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,39 +1515,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582893</v>
+        <v>582796</v>
       </c>
       <c r="R9" t="n">
-        <v>7041163</v>
+        <v>7041306</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1584,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,22 +1599,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122846952</v>
+        <v>122847371</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
+        <v>90975</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,39 +1627,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582892</v>
+        <v>582809</v>
       </c>
       <c r="R10" t="n">
-        <v>7041245</v>
+        <v>7041285</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,12 +1696,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:51</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,12 +1711,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1726,7 +1726,7 @@
         <v>123271869</v>
       </c>
       <c r="B11" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 4005-2025 artfynd.xlsx
+++ b/artfynd/A 4005-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122846313</v>
+        <v>122847452</v>
       </c>
       <c r="B2" t="n">
-        <v>78771</v>
+        <v>82559</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582953</v>
+        <v>582796</v>
       </c>
       <c r="R2" t="n">
-        <v>7041141</v>
+        <v>7041306</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122846482</v>
+        <v>122846587</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -823,7 +823,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582919</v>
+        <v>582893</v>
       </c>
       <c r="R3" t="n">
-        <v>7041138</v>
+        <v>7041163</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,11 +880,6 @@
           <t>15:38</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -897,22 +892,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122847974</v>
+        <v>122846482</v>
       </c>
       <c r="B4" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,34 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582679</v>
+        <v>582919</v>
       </c>
       <c r="R4" t="n">
-        <v>7041287</v>
+        <v>7041138</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122846587</v>
+        <v>122846952</v>
       </c>
       <c r="B5" t="n">
-        <v>57497</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,16 +1042,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1066,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582893</v>
+        <v>582892</v>
       </c>
       <c r="R5" t="n">
-        <v>7041163</v>
+        <v>7041245</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1116,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122846952</v>
+        <v>122846313</v>
       </c>
       <c r="B6" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,39 +1164,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582892</v>
+        <v>582953</v>
       </c>
       <c r="R6" t="n">
-        <v>7041245</v>
+        <v>7041141</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,12 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:51</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,22 +1248,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122846792</v>
+        <v>122847974</v>
       </c>
       <c r="B7" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,39 +1276,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582913</v>
+        <v>582679</v>
       </c>
       <c r="R7" t="n">
-        <v>7041182</v>
+        <v>7041287</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,12 +1345,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122847763</v>
+        <v>122847371</v>
       </c>
       <c r="B8" t="n">
-        <v>57497</v>
+        <v>90981</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,39 +1388,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582749</v>
+        <v>582809</v>
       </c>
       <c r="R8" t="n">
-        <v>7041278</v>
+        <v>7041285</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1472,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122847452</v>
+        <v>122846792</v>
       </c>
       <c r="B9" t="n">
-        <v>82558</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,34 +1500,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582796</v>
+        <v>582913</v>
       </c>
       <c r="R9" t="n">
-        <v>7041306</v>
+        <v>7041182</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1574,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1574,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,10 +1606,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122847371</v>
+        <v>122847763</v>
       </c>
       <c r="B10" t="n">
-        <v>90975</v>
+        <v>57497</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,34 +1622,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582809</v>
+        <v>582749</v>
       </c>
       <c r="R10" t="n">
-        <v>7041285</v>
+        <v>7041278</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1726,7 +1726,7 @@
         <v>123271869</v>
       </c>
       <c r="B11" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 4005-2025 artfynd.xlsx
+++ b/artfynd/A 4005-2025 artfynd.xlsx
@@ -1726,7 +1726,7 @@
         <v>123271869</v>
       </c>
       <c r="B11" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 4005-2025 artfynd.xlsx
+++ b/artfynd/A 4005-2025 artfynd.xlsx
@@ -1726,7 +1726,7 @@
         <v>123271869</v>
       </c>
       <c r="B11" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 4005-2025 artfynd.xlsx
+++ b/artfynd/A 4005-2025 artfynd.xlsx
@@ -1726,7 +1726,7 @@
         <v>123271869</v>
       </c>
       <c r="B11" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
